--- a/EXCEL/Exercise Files/Chapter01/01_02_Minimums.xlsx
+++ b/EXCEL/Exercise Files/Chapter01/01_02_Minimums.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Curtis\Desktop\Exercise Files\Chapter01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\neha work\Data Analytics\EXCEL\Exercise Files\Chapter01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{648F40EA-204A-4FC7-AD1B-3843D17EB7F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F231F072-5649-4F0B-93A9-CBE207961B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="12549" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -23,6 +23,10 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -55,7 +59,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -100,7 +104,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -108,7 +112,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -391,229 +395,244 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D40"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.69140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.84375" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1684</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="D2" s="3">
+        <f>MIN(A2:A40)</f>
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1738</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1861</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="D4" s="3">
+        <f>MAX(A2:A40)</f>
+        <v>9932</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>2392</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>2511</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="D6" s="3">
+        <f>_xlfn.QUARTILE.EXC(A2:A40,1)</f>
+        <v>4293</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>2780</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>3547</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="D8" s="3">
+        <f>_xlfn.QUARTILE.EXC(A2:A40,2)</f>
+        <v>6062</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>3741</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>4109</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="D10" s="3">
+        <f>_xlfn.QUARTILE.EXC(A2:A40,3)</f>
+        <v>7491</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>4293</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>4316</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>4364</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>4465</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>4479</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>4521</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>4754</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>5099</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>5629</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>5786</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>6062</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>6221</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>6231</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>6286</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>6424</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>6885</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>6898</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>6955</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>7265</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>7330</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>7491</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>7641</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>7666</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>7751</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>8060</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>8219</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>8283</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>8852</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>9637</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>9932</v>
       </c>
